--- a/data/merged/2026-10-08/MERGED_ES_Wet-Dry-Floor-Washer_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_ES_Wet-Dry-Floor-Washer_2026-10-08.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR8"/>
+  <dimension ref="A1:BR7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2347,40 +2347,40 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B0D2KT41N3</t>
+          <t>B0H9LQCPJ9</t>
         </is>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspiradora con Cable en Seco y Húmedos - Aspirador Sólidos y Líquidos 16L Conga Rockstar Wet &amp; Dry Compact Garden Plu</t>
+          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF61BS, sin Cable, en NegrosAspira y friega en una sola pasada eliminando sucie</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0D2KT41N3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H9LQCPJ9?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61i3ER7HQGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B0D2KT41N3</t>
+          <t>B0H9LQCPJ9</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="O5" s="15">
-        <v>3671</v>
+        <v>428292</v>
       </c>
       <c r="P5" s="15">
-        <v>-79</v>
+        <v>-353878</v>
       </c>
       <c r="Q5" s="16">
-        <v>-0.02</v>
+        <v>-5.44</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -2409,94 +2409,74 @@
       </c>
       <c r="S5" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T5" s="15">
-        <v>430</v>
-      </c>
-      <c r="U5" s="16">
-        <v>0.24</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U5" s="16"/>
       <c r="V5" s="15">
-        <v>19307</v>
-      </c>
-      <c r="W5" s="15" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="X5" s="15">
-        <v>12522</v>
-      </c>
+        <v>998</v>
+      </c>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
       <c r="Y5" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z5" s="20">
-        <v>37.11</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z5" s="20"/>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="19">
-        <v>959</v>
+        <v>50</v>
       </c>
       <c r="AE5" s="15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF5" s="21">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AG5" s="22">
-        <v>0.0837</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="20">
-        <v>10.1</v>
+        <v>12.61</v>
       </c>
       <c r="AI5" s="16">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="AJ5"/>
       <c r="AK5" s="13" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AL5" s="19">
-        <v>895</v>
+        <v>63</v>
       </c>
       <c r="AM5" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN5" s="13"/>
       <c r="AO5" s="13"/>
       <c r="AP5"/>
-      <c r="AQ5" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ5" s="19"/>
       <c r="AR5" s="19">
         <v>1</v>
       </c>
-      <c r="AS5" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="AS5" s="14"/>
       <c r="AT5" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU5" s="13"/>
       <c r="AV5" s="14"/>
       <c r="AW5" s="13"/>
-      <c r="AX5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AX5" s="13"/>
       <c r="AY5" s="13"/>
       <c r="AZ5" s="13"/>
       <c r="BA5" s="13"/>
@@ -2506,11 +2486,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD5" s="13"/>
       <c r="BE5" s="13"/>
       <c r="BF5" s="13"/>
       <c r="BG5" s="13"/>
@@ -2518,42 +2494,42 @@
       <c r="BI5"/>
       <c r="BJ5" s="23" t="inlineStr">
         <is>
-          <t>4.5 kg</t>
+          <t>8.5 kg</t>
         </is>
       </c>
       <c r="BK5" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>8.50 kg</t>
         </is>
       </c>
       <c r="BL5" s="23" t="inlineStr">
         <is>
-          <t>38 x 33 x 45 cm</t>
+          <t>78.8 x 32.5 x 34.8 cm</t>
         </is>
       </c>
       <c r="BM5" s="23" t="inlineStr">
         <is>
-          <t>38.00 x 33.00 x 45.00 cm</t>
+          <t>78.80 x 32.50 x 34.80 cm</t>
         </is>
       </c>
       <c r="BN5" s="23" t="inlineStr">
         <is>
-          <t>5.37 kg</t>
+          <t>11 kg</t>
         </is>
       </c>
       <c r="BO5" s="23" t="inlineStr">
         <is>
-          <t>5.37 kg</t>
+          <t>11.00 kg</t>
         </is>
       </c>
       <c r="BP5" s="23" t="inlineStr">
         <is>
-          <t>40 x 36 x 36 cm</t>
+          <t>78.5 x 34 x 32 cm</t>
         </is>
       </c>
       <c r="BQ5" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 36.00 x 36.00 cm</t>
+          <t>78.50 x 34.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BR5" s="13" t="inlineStr">
@@ -2569,40 +2545,40 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0H9LQCPJ9</t>
+          <t>B0DGV9F4X3</t>
         </is>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Rowenta</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF61BS, sin Cable, en NegrosAspira y friega en una sola pasada eliminando sucie</t>
+          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, NegrosAspira y Friega a la vez, 200 W, Pantalla De Control Intel</t>
         </is>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H9LQCPJ9?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61i3ER7HQGL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0H9LQCPJ9</t>
+          <t>B0DGV9F4X3</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
@@ -2616,66 +2592,70 @@
         </is>
       </c>
       <c r="O6" s="15">
-        <v>428292</v>
-      </c>
-      <c r="P6" s="15">
-        <v>-353878</v>
-      </c>
+        <v>240028</v>
+      </c>
+      <c r="P6" s="15"/>
       <c r="Q6" s="16">
-        <v>-5.44</v>
+        <v>0</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
-          <t>Aspiradoras domésticas para sólidos y líquidos</t>
+          <t>Aspiradoras
+Aspiradoras domésticas para sólidos y líquidos
+Aspiradoras en seco y húmedo
+Aspiradoras verticales
+Volver a los resultados
+Aspiradoras escoba</t>
         </is>
       </c>
       <c r="S6" s="18" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T6" s="15">
-        <v>2</v>
-      </c>
+          <t>41
+6
+10
+9
+5766
+18</t>
+        </is>
+      </c>
+      <c r="T6" s="15"/>
       <c r="U6" s="16"/>
-      <c r="V6" s="15">
-        <v>998</v>
-      </c>
+      <c r="V6" s="15"/>
       <c r="W6" s="15"/>
       <c r="X6" s="15"/>
       <c r="Y6" s="19">
         <v>1</v>
       </c>
-      <c r="Z6" s="20"/>
+      <c r="Z6" s="20">
+        <v>159.56</v>
+      </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="19">
-        <v>50</v>
+        <v>834</v>
       </c>
       <c r="AE6" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AF6" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG6" s="22">
         <v>0</v>
       </c>
-      <c r="AH6" s="20">
-        <v>12.61</v>
-      </c>
+      <c r="AH6" s="20"/>
       <c r="AI6" s="16">
         <v>0</v>
       </c>
       <c r="AJ6"/>
       <c r="AK6" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AL6" s="19">
-        <v>63</v>
+        <v>701</v>
       </c>
       <c r="AM6" s="13" t="inlineStr">
         <is>
@@ -2687,9 +2667,13 @@
       <c r="AP6"/>
       <c r="AQ6" s="19"/>
       <c r="AR6" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS6" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="AS6" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="AT6" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -2716,49 +2700,25 @@
       <c r="BI6"/>
       <c r="BJ6" s="23" t="inlineStr">
         <is>
-          <t>8.5 kg</t>
+          <t>5,4 kg</t>
         </is>
       </c>
       <c r="BK6" s="23" t="inlineStr">
         <is>
-          <t>8.50 kg</t>
+          <t>5.40 kg</t>
         </is>
       </c>
       <c r="BL6" s="23" t="inlineStr">
         <is>
-          <t>78.8 x 32.5 x 34.8 cm</t>
-        </is>
-      </c>
-      <c r="BM6" s="23" t="inlineStr">
-        <is>
-          <t>78.80 x 32.50 x 34.80 cm</t>
-        </is>
-      </c>
-      <c r="BN6" s="23" t="inlineStr">
-        <is>
-          <t>11 kg</t>
-        </is>
-      </c>
-      <c r="BO6" s="23" t="inlineStr">
-        <is>
-          <t>11.00 kg</t>
-        </is>
-      </c>
-      <c r="BP6" s="23" t="inlineStr">
-        <is>
-          <t>78.5 x 34 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BQ6" s="23" t="inlineStr">
-        <is>
-          <t>78.50 x 34.00 x 32.00 cm</t>
-        </is>
-      </c>
-      <c r="BR6" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+          <t>31,5l. x 30,5an. x 114,7al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM6" s="23"/>
+      <c r="BN6" s="23"/>
+      <c r="BO6" s="23"/>
+      <c r="BP6" s="23"/>
+      <c r="BQ6" s="23"/>
+      <c r="BR6" s="13"/>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
@@ -2767,40 +2727,40 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B0DGV9F4X3</t>
+          <t>B0H9LVZZV1</t>
         </is>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Rowenta</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, NegrosAspira y Friega a la vez, 200 W, Pantalla De Control Intel</t>
+          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF41WS, sin Cable, BlancosAspira y friega de una pasada, autolimpieza, sistema</t>
         </is>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H9LVZZV1?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B0DGV9F4X3</t>
+          <t>B0H9LVZZV1</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
@@ -2814,34 +2774,28 @@
         </is>
       </c>
       <c r="O7" s="15">
-        <v>240028</v>
-      </c>
-      <c r="P7" s="15"/>
+        <v>506279</v>
+      </c>
+      <c r="P7" s="15">
+        <v>-83489</v>
+      </c>
       <c r="Q7" s="16">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
-          <t>Aspiradoras
-Aspiradoras domésticas para sólidos y líquidos
-Aspiradoras en seco y húmedo
-Aspiradoras verticales
-Volver a los resultados
-Aspiradoras escoba</t>
+          <t>Aspiradoras domésticas para sólidos y líquidos</t>
         </is>
       </c>
       <c r="S7" s="18" t="inlineStr">
         <is>
-          <t>41
-6
-10
-9
-5766
-18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T7" s="15"/>
-      <c r="U7" s="16"/>
+      <c r="U7" s="16">
+        <v>-0.62</v>
+      </c>
       <c r="V7" s="15"/>
       <c r="W7" s="15"/>
       <c r="X7" s="15"/>
@@ -2849,35 +2803,37 @@
         <v>1</v>
       </c>
       <c r="Z7" s="20">
-        <v>159.56</v>
+        <v>299.99</v>
       </c>
       <c r="AA7"/>
       <c r="AB7"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="19">
-        <v>834</v>
+        <v>48</v>
       </c>
       <c r="AE7" s="15">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AF7" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG7" s="22">
         <v>0</v>
       </c>
-      <c r="AH7" s="20"/>
+      <c r="AH7" s="20">
+        <v>12.61</v>
+      </c>
       <c r="AI7" s="16">
-        <v>0</v>
+        <v>0.81</v>
       </c>
       <c r="AJ7"/>
       <c r="AK7" s="13" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AL7" s="19">
-        <v>701</v>
+        <v>58</v>
       </c>
       <c r="AM7" s="13" t="inlineStr">
         <is>
@@ -2889,7 +2845,7 @@
       <c r="AP7"/>
       <c r="AQ7" s="19"/>
       <c r="AR7" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS7" s="14" t="inlineStr">
         <is>
@@ -2922,223 +2878,45 @@
       <c r="BI7"/>
       <c r="BJ7" s="23" t="inlineStr">
         <is>
-          <t>5,4 kg</t>
+          <t>8.5 kg</t>
         </is>
       </c>
       <c r="BK7" s="23" t="inlineStr">
         <is>
-          <t>5.40 kg</t>
+          <t>8.50 kg</t>
         </is>
       </c>
       <c r="BL7" s="23" t="inlineStr">
         <is>
-          <t>31,5l. x 30,5an. x 114,7al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM7" s="23"/>
-      <c r="BN7" s="23"/>
-      <c r="BO7" s="23"/>
-      <c r="BP7" s="23"/>
-      <c r="BQ7" s="23"/>
-      <c r="BR7" s="13"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>B0H9LVZZV1</t>
-        </is>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF41WS, sin Cable, BlancosAspira y friega de una pasada, autolimpieza, sistema</t>
-        </is>
-      </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0H9LVZZV1?psc=1</t>
-        </is>
-      </c>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>B0H9LVZZV1</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O8" s="15">
-        <v>506279</v>
-      </c>
-      <c r="P8" s="15">
-        <v>-83489</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>-0.2</v>
-      </c>
-      <c r="R8" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="S8" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T8" s="15"/>
-      <c r="U8" s="16">
-        <v>-0.62</v>
-      </c>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="20">
-        <v>299.99</v>
-      </c>
-      <c r="AA8"/>
-      <c r="AB8"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="19">
-        <v>48</v>
-      </c>
-      <c r="AE8" s="15">
-        <v>40</v>
-      </c>
-      <c r="AF8" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG8" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="20">
-        <v>12.61</v>
-      </c>
-      <c r="AI8" s="16">
-        <v>0.81</v>
-      </c>
-      <c r="AJ8"/>
-      <c r="AK8" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AL8" s="19">
-        <v>58</v>
-      </c>
-      <c r="AM8" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN8" s="13"/>
-      <c r="AO8" s="13"/>
-      <c r="AP8"/>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS8" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT8" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU8" s="13"/>
-      <c r="AV8" s="14"/>
-      <c r="AW8" s="13"/>
-      <c r="AX8" s="13"/>
-      <c r="AY8" s="13"/>
-      <c r="AZ8" s="13"/>
-      <c r="BA8" s="13"/>
-      <c r="BB8" s="13"/>
-      <c r="BC8" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD8" s="13"/>
-      <c r="BE8" s="13"/>
-      <c r="BF8" s="13"/>
-      <c r="BG8" s="13"/>
-      <c r="BH8" s="14"/>
-      <c r="BI8"/>
-      <c r="BJ8" s="23" t="inlineStr">
-        <is>
-          <t>8.5 kg</t>
-        </is>
-      </c>
-      <c r="BK8" s="23" t="inlineStr">
-        <is>
-          <t>8.50 kg</t>
-        </is>
-      </c>
-      <c r="BL8" s="23" t="inlineStr">
-        <is>
           <t>78.8 x 32.5 x 34.8 cm</t>
         </is>
       </c>
-      <c r="BM8" s="23" t="inlineStr">
+      <c r="BM7" s="23" t="inlineStr">
         <is>
           <t>78.80 x 32.50 x 34.80 cm</t>
         </is>
       </c>
-      <c r="BN8" s="23" t="inlineStr">
+      <c r="BN7" s="23" t="inlineStr">
         <is>
           <t>10.51 kg</t>
         </is>
       </c>
-      <c r="BO8" s="23" t="inlineStr">
+      <c r="BO7" s="23" t="inlineStr">
         <is>
           <t>10.51 kg</t>
         </is>
       </c>
-      <c r="BP8" s="23" t="inlineStr">
+      <c r="BP7" s="23" t="inlineStr">
         <is>
           <t>79 x 34 x 32 cm</t>
         </is>
       </c>
-      <c r="BQ8" s="23" t="inlineStr">
+      <c r="BQ7" s="23" t="inlineStr">
         <is>
           <t>79.00 x 34.00 x 32.00 cm</t>
         </is>
       </c>
-      <c r="BR8" s="13" t="inlineStr">
+      <c r="BR7" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
@@ -3169,42 +2947,35 @@
     <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.es/dp/B0DHHG7P99"/>
     <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N4" r:id="rId21"/>
-    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
-    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0D2KT41N3?psc=1"/>
-    <hyperlink ref="K5" r:id="rId25" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg"/>
-    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
+    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
+    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9?psc=1"/>
+    <hyperlink ref="K5" r:id="rId25" tooltip="https://images-na.ssl-images-amazon.com/images/I/61i3ER7HQGL._AC_US600_.jpg"/>
+    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
     <hyperlink ref="M5" r:id="rId27" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N5" r:id="rId28"/>
-    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
-    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9?psc=1"/>
-    <hyperlink ref="K6" r:id="rId32" tooltip="https://images-na.ssl-images-amazon.com/images/I/61i3ER7HQGL._AC_US600_.jpg"/>
-    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
+    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
+    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
+    <hyperlink ref="K6" r:id="rId32" tooltip="https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg"/>
+    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
     <hyperlink ref="M6" r:id="rId34" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N6" r:id="rId35"/>
-    <hyperlink ref="C7" r:id="rId36" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
-    <hyperlink ref="G7" r:id="rId37" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
-    <hyperlink ref="K7" r:id="rId39" tooltip="https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg"/>
-    <hyperlink ref="L7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
+    <hyperlink ref="C7" r:id="rId36" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
+    <hyperlink ref="G7" r:id="rId37" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0H9LVZZV1?psc=1"/>
+    <hyperlink ref="K7" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg"/>
+    <hyperlink ref="L7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
     <hyperlink ref="M7" r:id="rId41" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N7" r:id="rId42"/>
-    <hyperlink ref="C8" r:id="rId43" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
-    <hyperlink ref="G8" r:id="rId44" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J8" r:id="rId45" tooltip="https://www.amazon.es/dp/B0H9LVZZV1?psc=1"/>
-    <hyperlink ref="K8" r:id="rId46" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg"/>
-    <hyperlink ref="L8" r:id="rId47" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
-    <hyperlink ref="M8" r:id="rId48" tooltip="https://www.amazon.es/b?node=218878925031"/>
-    <hyperlink ref="N8" r:id="rId49"/>
   </hyperlinks>
-  <drawing r:id="rId50"/>
+  <drawing r:id="rId43"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -3268,7 +3039,7 @@
         <v>259.0</v>
       </c>
       <c r="G2" s="22">
-        <v>0.5381493506493507</v>
+        <v>0.8266832917705735</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3289,49 +3060,28 @@
         <v>378.036496350365</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1112012987012987</v>
+        <v>0.1708229426433915</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B4" s="15">
-        <v>430</v>
+        <v>2</v>
       </c>
       <c r="C4" s="15">
-        <v>19307</v>
+        <v>998</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>44.9</v>
+        <v>499.0</v>
       </c>
       <c r="G4" s="22">
-        <v>0.349025974025974</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="B5" s="15">
-        <v>2</v>
-      </c>
-      <c r="C5" s="15">
-        <v>998</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="20">
-        <v>499.0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.0016233766233766235</v>
+        <v>0.0024937655860349127</v>
       </c>
     </row>
   </sheetData>
@@ -3395,18 +3145,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>1230</v>
+        <v>800</v>
       </c>
       <c r="C2" s="15">
-        <v>242815</v>
+        <v>223508</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>197.41056910569105</v>
+        <v>279.385</v>
       </c>
       <c r="G2" s="22">
-        <v>0.9983766233766234</v>
+        <v>0.9975062344139651</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3427,7 +3177,7 @@
         <v>499.0</v>
       </c>
       <c r="G3" s="22">
-        <v>0.0016233766233766235</v>
+        <v>0.0024937655860349127</v>
       </c>
     </row>
   </sheetData>
